--- a/運営指導対応_2026年度/01_法定研修_年間計画・管理表_2026年度.xlsx
+++ b/運営指導対応_2026年度/01_法定研修_年間計画・管理表_2026年度.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>鈴木　※運営基準で「担当者を定めること」が義務。氏名を事業所内に掲示すること</t>
+          <t>鈴木　菜緒子　※運営基準で「担当者を定めること」が義務。氏名を事業所内に掲示すること</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>川島　宏太（第一窓口）／第二窓口・外部窓口は要設定</t>
+          <t>川島　宏太（内部窓口）／顧問社会保険労務士（外部窓口。管理者自身に関する相談はこちら）</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -2170,7 +2170,7 @@
       <c r="C8" s="17" t="inlineStr">
         <is>
           <t>高齢者虐待の防止／身体的拘束等の適正化 研修
-・虐待の5類型と通報義務（通報先：上尾市介護保険課）
+・虐待の5類型と通報義務（通報先：上尾市 高齢介護課）
 ・在宅での身体的拘束の具体例と3要件
 ・記録の書き方の演習
 ※終了後に虐待防止委員会（第1回）を開催</t>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>鈴木</t>
+          <t>鈴木　菜緒子</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
